--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8447,0.1185,0.0063,0.0162</t>
-  </si>
-  <si>
-    <t>0.0457,0.0329,0.0117,0.9643</t>
-  </si>
-  <si>
-    <t>0.6741,0.0067,0.0014,0.4385</t>
-  </si>
-  <si>
-    <t>0.0456,0.0220,0.0076,0.9739</t>
-  </si>
-  <si>
-    <t>0.9964,0.0013,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0194,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9935,0.0058,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9894,0.0109,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9490,0.0848,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9970,0.0007,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.5857,0.1060,0.2999,0.0038</t>
-  </si>
-  <si>
-    <t>0.2014,0.0411,0.8267,0.0057</t>
-  </si>
-  <si>
-    <t>0.2089,0.0252,0.8555,0.0003</t>
-  </si>
-  <si>
-    <t>0.1391,0.0138,0.8889,0.0042</t>
-  </si>
-  <si>
-    <t>0.3248,0.2278,0.4973,0.0031</t>
-  </si>
-  <si>
-    <t>0.0060,0.9909,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0197,0.9793,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.2492,0.7930,0.0246,0.0051</t>
-  </si>
-  <si>
-    <t>0.0037,0.9920,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0043,0.9922,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.6618,0.0078,0.3069,0.0307</t>
-  </si>
-  <si>
-    <t>0.3074,0.0198,0.7440,0.0079</t>
-  </si>
-  <si>
-    <t>0.0542,0.0070,0.9408,0.0054</t>
-  </si>
-  <si>
-    <t>0.3041,0.1775,0.4384,0.0426</t>
-  </si>
-  <si>
-    <t>0.0077,0.0502,0.9736,0.0034</t>
-  </si>
-  <si>
-    <t>0.0925,0.0338,0.8786,0.0088</t>
-  </si>
-  <si>
-    <t>0.0010,0.0016,0.9949,0.0051</t>
-  </si>
-  <si>
-    <t>0.4720,0.5529,0.0132,0.0117</t>
-  </si>
-  <si>
-    <t>0.5568,0.2425,0.2981,0.0107</t>
-  </si>
-  <si>
-    <t>0.0021,0.0040,0.9944,0.0012</t>
-  </si>
-  <si>
-    <t>0.0012,0.9815,0.0709,0.0000</t>
-  </si>
-  <si>
-    <t>0.8747,0.1165,0.0153,0.0074</t>
-  </si>
-  <si>
-    <t>0.5346,0.0800,0.3998,0.0055</t>
-  </si>
-  <si>
-    <t>0.4492,0.4606,0.0984,0.0008</t>
-  </si>
-  <si>
-    <t>0.0801,0.7896,0.4444,0.0254</t>
-  </si>
-  <si>
-    <t>0.0094,0.7189,0.5696,0.0031</t>
-  </si>
-  <si>
-    <t>0.0499,0.0167,0.8899,0.0815</t>
-  </si>
-  <si>
-    <t>0.0811,0.1207,0.8899,0.0070</t>
-  </si>
-  <si>
-    <t>0.1285,0.0107,0.8564,0.0292</t>
-  </si>
-  <si>
-    <t>0.0365,0.6689,0.7501,0.0149</t>
-  </si>
-  <si>
-    <t>0.0147,0.8197,0.1835,0.0007</t>
-  </si>
-  <si>
-    <t>0.0020,0.0728,0.9869,0.0018</t>
-  </si>
-  <si>
-    <t>0.1056,0.7480,0.0345,0.2860</t>
-  </si>
-  <si>
-    <t>0.0065,0.9531,0.0074,0.0474</t>
-  </si>
-  <si>
-    <t>0.0094,0.9602,0.0829,0.0010</t>
-  </si>
-  <si>
-    <t>0.0029,0.9778,0.2234,0.0005</t>
-  </si>
-  <si>
-    <t>0.0072,0.0680,0.9491,0.0176</t>
-  </si>
-  <si>
-    <t>0.0009,0.0360,0.9916,0.0012</t>
-  </si>
-  <si>
-    <t>0.0209,0.0089,0.9582,0.0158</t>
-  </si>
-  <si>
-    <t>0.0085,0.0018,0.9921,0.0005</t>
-  </si>
-  <si>
-    <t>0.0034,0.0128,0.9922,0.0003</t>
-  </si>
-  <si>
-    <t>0.0191,0.0556,0.9722,0.0007</t>
-  </si>
-  <si>
-    <t>0.9718,0.0490,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9803,0.0138,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.9529,0.0701,0.0043,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0088,0.9953,0.0023</t>
-  </si>
-  <si>
-    <t>0.9844,0.0064,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.9742,0.0219,0.0057,0.0006</t>
-  </si>
-  <si>
-    <t>0.9582,0.0461,0.0055,0.0017</t>
-  </si>
-  <si>
-    <t>0.0011,0.6957,0.9780,0.0004</t>
-  </si>
-  <si>
-    <t>0.0291,0.0244,0.9590,0.0018</t>
-  </si>
-  <si>
-    <t>0.0030,0.0382,0.9649,0.0130</t>
-  </si>
-  <si>
-    <t>0.0007,0.9377,0.9473,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.0030,0.9863,0.0161</t>
-  </si>
-  <si>
-    <t>0.0498,0.8547,0.1035,0.0010</t>
-  </si>
-  <si>
-    <t>0.0248,0.9630,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.8078,0.0389,0.2286,0.0123</t>
-  </si>
-  <si>
-    <t>0.6635,0.2621,0.1316,0.0279</t>
-  </si>
-  <si>
-    <t>0.0025,0.0205,0.9900,0.0004</t>
-  </si>
-  <si>
-    <t>0.0125,0.4068,0.8572,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.8350,0.9619,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9837,0.5927,0.0006</t>
-  </si>
-  <si>
-    <t>0.0027,0.8473,0.8671,0.0006</t>
-  </si>
-  <si>
-    <t>0.0147,0.0006,0.0996,0.9478</t>
-  </si>
-  <si>
-    <t>0.0082,0.0044,0.0003,0.9963</t>
-  </si>
-  <si>
-    <t>0.0250,0.0020,0.0004,0.9924</t>
-  </si>
-  <si>
-    <t>0.0101,0.0091,0.0159,0.9876</t>
-  </si>
-  <si>
-    <t>0.0033,0.0014,0.0042,0.9967</t>
-  </si>
-  <si>
-    <t>0.0085,0.0044,0.0049,0.9933</t>
-  </si>
-  <si>
-    <t>0.0011,0.9431,0.8972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0031,0.3972,0.9755,0.0001</t>
-  </si>
-  <si>
-    <t>0.0202,0.3256,0.8962,0.0011</t>
-  </si>
-  <si>
-    <t>0.0094,0.7723,0.8212,0.0043</t>
-  </si>
-  <si>
-    <t>0.0008,0.9385,0.8085,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.7576,0.8774,0.0005</t>
-  </si>
-  <si>
-    <t>0.9925,0.0037,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9824,0.0351,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9360,0.0794,0.0116,0.0008</t>
-  </si>
-  <si>
-    <t>0.9767,0.0133,0.0009,0.0041</t>
-  </si>
-  <si>
-    <t>0.9679,0.0568,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9907,0.0065,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9799,0.0181,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.9701,0.0448,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0027,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0015,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9927,0.0033,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9925,0.0048,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9962,0.0026,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9881,0.0068,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0246,0.0080,0.9775,0.0011</t>
-  </si>
-  <si>
-    <t>0.4895,0.0036,0.7302,0.0004</t>
-  </si>
-  <si>
-    <t>0.7026,0.0081,0.3691,0.0081</t>
-  </si>
-  <si>
-    <t>0.0280,0.0021,0.9844,0.0003</t>
-  </si>
-  <si>
-    <t>0.0221,0.9725,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.0032,0.9931,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.1393,0.8845,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.0898,0.9049,0.0039,0.0058</t>
-  </si>
-  <si>
-    <t>0.0294,0.9646,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.0061,0.9878,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.6228,0.4793,0.0178,0.0013</t>
-  </si>
-  <si>
-    <t>0.5960,0.1898,0.2533,0.0092</t>
-  </si>
-  <si>
-    <t>0.1113,0.0179,0.8862,0.0139</t>
-  </si>
-  <si>
-    <t>0.2249,0.4366,0.4030,0.0173</t>
-  </si>
-  <si>
-    <t>0.3731,0.0432,0.6906,0.0023</t>
-  </si>
-  <si>
-    <t>0.0337,0.3446,0.0717,0.8803</t>
-  </si>
-  <si>
-    <t>0.0307,0.9526,0.0193,0.0027</t>
-  </si>
-  <si>
-    <t>0.0064,0.9720,0.0133,0.0091</t>
-  </si>
-  <si>
-    <t>0.0227,0.9214,0.0149,0.0533</t>
-  </si>
-  <si>
-    <t>0.0024,0.8651,0.8987,0.0008</t>
-  </si>
-  <si>
-    <t>0.0026,0.9889,0.0718,0.0001</t>
-  </si>
-  <si>
-    <t>0.7234,0.2755,0.0446,0.0016</t>
-  </si>
-  <si>
-    <t>0.7338,0.3114,0.0401,0.0040</t>
-  </si>
-  <si>
-    <t>0.9468,0.0514,0.0081,0.0023</t>
-  </si>
-  <si>
-    <t>0.9916,0.0017,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.9891,0.0005,0.0001,0.0079</t>
-  </si>
-  <si>
-    <t>0.9690,0.0248,0.0048,0.0021</t>
-  </si>
-  <si>
-    <t>0.9899,0.0025,0.0009,0.0020</t>
-  </si>
-  <si>
-    <t>0.9642,0.0128,0.0122,0.0039</t>
-  </si>
-  <si>
-    <t>0.9837,0.0052,0.0029,0.0025</t>
-  </si>
-  <si>
-    <t>0.9897,0.0047,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.0060,0.5442,0.9403,0.0025</t>
-  </si>
-  <si>
-    <t>0.0005,0.8021,0.9512,0.0000</t>
-  </si>
-  <si>
-    <t>0.0142,0.1567,0.9450,0.0054</t>
-  </si>
-  <si>
-    <t>0.0047,0.4329,0.9544,0.0002</t>
-  </si>
-  <si>
-    <t>0.7910,0.0608,0.0816,0.0323</t>
-  </si>
-  <si>
-    <t>0.8469,0.0760,0.0403,0.0074</t>
-  </si>
-  <si>
-    <t>0.5656,0.0116,0.5612,0.0083</t>
-  </si>
-  <si>
-    <t>0.5978,0.1904,0.1715,0.0828</t>
-  </si>
-  <si>
-    <t>0.4452,0.0012,0.0020,0.7393</t>
-  </si>
-  <si>
-    <t>0.0011,0.0017,0.0009,0.9989</t>
-  </si>
-  <si>
-    <t>0.0034,0.0428,0.0006,0.9946</t>
-  </si>
-  <si>
-    <t>0.0250,0.0007,0.0064,0.9859</t>
-  </si>
-  <si>
-    <t>0.0028,0.9642,0.2031,0.0004</t>
-  </si>
-  <si>
-    <t>0.9770,0.0155,0.0071,0.0008</t>
-  </si>
-  <si>
-    <t>0.6345,0.3846,0.0375,0.0060</t>
-  </si>
-  <si>
-    <t>0.9727,0.0038,0.0014,0.0121</t>
-  </si>
-  <si>
-    <t>0.5585,0.5789,0.0104,0.0006</t>
-  </si>
-  <si>
-    <t>0.9648,0.0027,0.0093,0.0091</t>
-  </si>
-  <si>
-    <t>0.4340,0.0109,0.0460,0.6279</t>
-  </si>
-  <si>
-    <t>0.9859,0.0024,0.0050,0.0016</t>
-  </si>
-  <si>
-    <t>0.0025,0.0286,0.9518,0.0753</t>
-  </si>
-  <si>
-    <t>0.9837,0.0003,0.0023,0.0064</t>
-  </si>
-  <si>
-    <t>0.9039,0.0075,0.0408,0.0411</t>
-  </si>
-  <si>
-    <t>0.3852,0.6191,0.0387,0.0283</t>
-  </si>
-  <si>
-    <t>0.6423,0.4026,0.0051,0.0072</t>
-  </si>
-  <si>
-    <t>0.8824,0.0501,0.0430,0.0087</t>
-  </si>
-  <si>
-    <t>0.3038,0.5021,0.0078,0.1008</t>
-  </si>
-  <si>
-    <t>0.7978,0.1020,0.0769,0.0137</t>
-  </si>
-  <si>
-    <t>0.7552,0.1516,0.0928,0.0030</t>
-  </si>
-  <si>
-    <t>0.9927,0.0022,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9924,0.0031,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9930,0.0022,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9818,0.0034,0.0044,0.0041</t>
-  </si>
-  <si>
-    <t>0.9935,0.0029,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9875,0.0066,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9814,0.0081,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.9846,0.0057,0.0008,0.0031</t>
-  </si>
-  <si>
-    <t>0.4306,0.5655,0.0114,0.0262</t>
-  </si>
-  <si>
-    <t>0.3356,0.6866,0.0390,0.0019</t>
-  </si>
-  <si>
-    <t>0.5188,0.6371,0.0068,0.0006</t>
-  </si>
-  <si>
-    <t>0.5979,0.2877,0.1670,0.0028</t>
-  </si>
-  <si>
-    <t>0.9761,0.0434,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.8054,0.2499,0.0192,0.0031</t>
-  </si>
-  <si>
-    <t>0.9431,0.0898,0.0039,0.0013</t>
-  </si>
-  <si>
-    <t>0.7389,0.3199,0.0173,0.0039</t>
-  </si>
-  <si>
-    <t>0.0023,0.0718,0.9908,0.0009</t>
-  </si>
-  <si>
-    <t>0.7126,0.2261,0.0917,0.0157</t>
-  </si>
-  <si>
-    <t>0.0068,0.0046,0.9934,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0423,0.9944,0.0003</t>
-  </si>
-  <si>
-    <t>0.1564,0.0120,0.8956,0.0048</t>
-  </si>
-  <si>
-    <t>0.0151,0.0411,0.9686,0.0018</t>
-  </si>
-  <si>
-    <t>0.0049,0.0065,0.9902,0.0006</t>
-  </si>
-  <si>
-    <t>0.0020,0.0021,0.9952,0.0007</t>
-  </si>
-  <si>
-    <t>0.0121,0.0028,0.9921,0.0001</t>
-  </si>
-  <si>
-    <t>0.4015,0.1593,0.4992,0.0157</t>
-  </si>
-  <si>
-    <t>0.0726,0.0268,0.9438,0.0005</t>
-  </si>
-  <si>
-    <t>0.4711,0.0465,0.6237,0.0030</t>
-  </si>
-  <si>
-    <t>0.1532,0.1971,0.6324,0.0009</t>
-  </si>
-  <si>
-    <t>0.3839,0.2331,0.3739,0.0058</t>
-  </si>
-  <si>
-    <t>0.4157,0.1008,0.4263,0.0005</t>
-  </si>
-  <si>
-    <t>0.1719,0.5308,0.3751,0.0193</t>
-  </si>
-  <si>
-    <t>0.5103,0.0228,0.5352,0.0338</t>
-  </si>
-  <si>
-    <t>0.8467,0.3182,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.7845,0.3148,0.0066,0.0005</t>
-  </si>
-  <si>
-    <t>0.8621,0.2428,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.9657,0.0375,0.0039,0.0009</t>
-  </si>
-  <si>
-    <t>0.8047,0.3481,0.0026,0.0012</t>
-  </si>
-  <si>
-    <t>0.6452,0.1317,0.2096,0.0144</t>
-  </si>
-  <si>
-    <t>0.8412,0.0037,0.2389,0.0031</t>
-  </si>
-  <si>
-    <t>0.6998,0.0055,0.1387,0.0837</t>
-  </si>
-  <si>
-    <t>0.4403,0.0083,0.6808,0.0098</t>
-  </si>
-  <si>
-    <t>0.8785,0.0139,0.0532,0.0198</t>
-  </si>
-  <si>
-    <t>0.0154,0.0232,0.9645,0.0064</t>
-  </si>
-  <si>
-    <t>0.0075,0.5507,0.6805,0.0437</t>
-  </si>
-  <si>
-    <t>0.0925,0.0710,0.8827,0.0049</t>
-  </si>
-  <si>
-    <t>0.1181,0.1427,0.8337,0.0082</t>
-  </si>
-  <si>
-    <t>0.0096,0.8749,0.1418,0.0064</t>
-  </si>
-  <si>
-    <t>0.9855,0.0082,0.0012,0.0018</t>
-  </si>
-  <si>
-    <t>0.9696,0.0295,0.0042,0.0015</t>
-  </si>
-  <si>
-    <t>0.9886,0.0093,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9913,0.0076,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9841,0.0083,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9866,0.0112,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9905,0.0029,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9835,0.0075,0.0027,0.0027</t>
-  </si>
-  <si>
-    <t>0.0136,0.0228,0.9771,0.0017</t>
-  </si>
-  <si>
-    <t>0.1333,0.5052,0.5971,0.0094</t>
-  </si>
-  <si>
-    <t>0.7947,0.0415,0.1524,0.0068</t>
-  </si>
-  <si>
-    <t>0.0032,0.0106,0.9909,0.0016</t>
-  </si>
-  <si>
-    <t>0.0014,0.0138,0.9946,0.0004</t>
-  </si>
-  <si>
-    <t>0.0132,0.1311,0.9386,0.0002</t>
-  </si>
-  <si>
-    <t>0.0052,0.0141,0.9884,0.0019</t>
-  </si>
-  <si>
-    <t>0.0396,0.0141,0.9506,0.0011</t>
-  </si>
-  <si>
-    <t>0.0026,0.0035,0.9952,0.0006</t>
-  </si>
-  <si>
-    <t>0.0015,0.0095,0.9656,0.0522</t>
-  </si>
-  <si>
-    <t>0.2900,0.0750,0.6819,0.0263</t>
-  </si>
-  <si>
-    <t>0.7123,0.0039,0.2989,0.0198</t>
-  </si>
-  <si>
-    <t>0.7664,0.0077,0.3553,0.0038</t>
-  </si>
-  <si>
-    <t>0.8649,0.0153,0.0794,0.0089</t>
-  </si>
-  <si>
-    <t>0.9932,0.0051,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9852,0.0176,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0023,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9804,0.0207,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0026,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9724,0.0452,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9928,0.0031,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9775,0.0097,0.0012,0.0047</t>
-  </si>
-  <si>
-    <t>0.1321,0.0487,0.8686,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.4658,0.9647,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.0174,0.9870,0.0014</t>
-  </si>
-  <si>
-    <t>0.0142,0.0039,0.9854,0.0010</t>
-  </si>
-  <si>
-    <t>0.0012,0.0291,0.9952,0.0002</t>
-  </si>
-  <si>
-    <t>0.0286,0.0101,0.9448,0.0335</t>
-  </si>
-  <si>
-    <t>0.1032,0.0095,0.9180,0.0040</t>
-  </si>
-  <si>
-    <t>0.0293,0.1751,0.8476,0.0873</t>
-  </si>
-  <si>
-    <t>0.9121,0.0008,0.0101,0.0513</t>
-  </si>
-  <si>
-    <t>0.0252,0.1049,0.0026,0.9756</t>
-  </si>
-  <si>
-    <t>0.0341,0.0024,0.0056,0.9830</t>
-  </si>
-  <si>
-    <t>0.0050,0.0007,0.0041,0.9956</t>
-  </si>
-  <si>
-    <t>0.0040,0.0068,0.0018,0.9967</t>
-  </si>
-  <si>
-    <t>0.7271,0.0222,0.0762,0.1875</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.6189,0.4082,0.0132,0.0187</t>
+  </si>
+  <si>
+    <t>0.0042,0.0107,0.0024,0.9961</t>
+  </si>
+  <si>
+    <t>0.8434,0.0066,0.0014,0.1473</t>
+  </si>
+  <si>
+    <t>0.4961,0.0007,0.0021,0.6660</t>
+  </si>
+  <si>
+    <t>0.9969,0.0014,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9871,0.0083,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9770,0.0257,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9901,0.0067,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0035,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9652,0.0570,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0023,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.5649,0.0284,0.5226,0.0025</t>
+  </si>
+  <si>
+    <t>0.4481,0.0061,0.7491,0.0011</t>
+  </si>
+  <si>
+    <t>0.4846,0.0812,0.5536,0.0094</t>
+  </si>
+  <si>
+    <t>0.0147,0.0121,0.9688,0.0029</t>
+  </si>
+  <si>
+    <t>0.2888,0.2906,0.4756,0.0353</t>
+  </si>
+  <si>
+    <t>0.0685,0.9468,0.0074,0.0016</t>
+  </si>
+  <si>
+    <t>0.0227,0.9755,0.0053,0.0015</t>
+  </si>
+  <si>
+    <t>0.5067,0.6004,0.0180,0.0032</t>
+  </si>
+  <si>
+    <t>0.0499,0.9523,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.0075,0.9828,0.0094,0.0007</t>
+  </si>
+  <si>
+    <t>0.6291,0.0037,0.3293,0.0169</t>
+  </si>
+  <si>
+    <t>0.5262,0.0194,0.5389,0.0087</t>
+  </si>
+  <si>
+    <t>0.2279,0.0081,0.8642,0.0017</t>
+  </si>
+  <si>
+    <t>0.2584,0.0186,0.7470,0.0405</t>
+  </si>
+  <si>
+    <t>0.2790,0.0120,0.7873,0.0040</t>
+  </si>
+  <si>
+    <t>0.2247,0.0034,0.8332,0.0076</t>
+  </si>
+  <si>
+    <t>0.0473,0.0089,0.9558,0.0015</t>
+  </si>
+  <si>
+    <t>0.5223,0.6156,0.0057,0.0010</t>
+  </si>
+  <si>
+    <t>0.2436,0.3198,0.5429,0.0030</t>
+  </si>
+  <si>
+    <t>0.0015,0.0047,0.9892,0.0121</t>
+  </si>
+  <si>
+    <t>0.0015,0.9835,0.0764,0.0001</t>
+  </si>
+  <si>
+    <t>0.8673,0.0607,0.0368,0.0155</t>
+  </si>
+  <si>
+    <t>0.5982,0.0421,0.4242,0.0095</t>
+  </si>
+  <si>
+    <t>0.3505,0.6392,0.0548,0.0012</t>
+  </si>
+  <si>
+    <t>0.0203,0.9524,0.0586,0.0032</t>
+  </si>
+  <si>
+    <t>0.0752,0.5642,0.3981,0.0120</t>
+  </si>
+  <si>
+    <t>0.1602,0.0857,0.7712,0.0652</t>
+  </si>
+  <si>
+    <t>0.0411,0.4399,0.7938,0.0608</t>
+  </si>
+  <si>
+    <t>0.2350,0.0124,0.4856,0.2370</t>
+  </si>
+  <si>
+    <t>0.1002,0.0921,0.8760,0.0023</t>
+  </si>
+  <si>
+    <t>0.0023,0.9578,0.0391,0.0043</t>
+  </si>
+  <si>
+    <t>0.0094,0.0348,0.9627,0.0156</t>
+  </si>
+  <si>
+    <t>0.1474,0.6492,0.0507,0.3791</t>
+  </si>
+  <si>
+    <t>0.0030,0.9757,0.0024,0.0268</t>
+  </si>
+  <si>
+    <t>0.0142,0.9489,0.0788,0.0056</t>
+  </si>
+  <si>
+    <t>0.0024,0.9896,0.0372,0.0003</t>
+  </si>
+  <si>
+    <t>0.0044,0.0624,0.9663,0.0071</t>
+  </si>
+  <si>
+    <t>0.0019,0.0754,0.9861,0.0005</t>
+  </si>
+  <si>
+    <t>0.0505,0.0502,0.9378,0.0013</t>
+  </si>
+  <si>
+    <t>0.0262,0.0107,0.9804,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.0185,0.9896,0.0006</t>
+  </si>
+  <si>
+    <t>0.0149,0.0092,0.9795,0.0021</t>
+  </si>
+  <si>
+    <t>0.9477,0.0949,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9561,0.0243,0.0212,0.0015</t>
+  </si>
+  <si>
+    <t>0.9458,0.0918,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.0322,0.9957,0.0006</t>
+  </si>
+  <si>
+    <t>0.9592,0.0213,0.0067,0.0058</t>
+  </si>
+  <si>
+    <t>0.9883,0.0190,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.8965,0.1639,0.0059,0.0013</t>
+  </si>
+  <si>
+    <t>0.0027,0.8394,0.9070,0.0015</t>
+  </si>
+  <si>
+    <t>0.0010,0.0384,0.9860,0.0047</t>
+  </si>
+  <si>
+    <t>0.0056,0.0183,0.9820,0.0038</t>
+  </si>
+  <si>
+    <t>0.0002,0.9238,0.9873,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0098,0.9926,0.0017</t>
+  </si>
+  <si>
+    <t>0.0722,0.8420,0.1232,0.0019</t>
+  </si>
+  <si>
+    <t>0.0041,0.9911,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.2046,0.1091,0.8260,0.0044</t>
+  </si>
+  <si>
+    <t>0.5630,0.4874,0.0595,0.0158</t>
+  </si>
+  <si>
+    <t>0.0081,0.0880,0.9672,0.0006</t>
+  </si>
+  <si>
+    <t>0.0031,0.7281,0.9644,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.6560,0.9739,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9774,0.4881,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.8678,0.9643,0.0001</t>
+  </si>
+  <si>
+    <t>0.0334,0.0070,0.2779,0.8738</t>
+  </si>
+  <si>
+    <t>0.0090,0.0081,0.0015,0.9938</t>
+  </si>
+  <si>
+    <t>0.0096,0.0058,0.0012,0.9949</t>
+  </si>
+  <si>
+    <t>0.0809,0.0105,0.0041,0.9583</t>
+  </si>
+  <si>
+    <t>0.0099,0.0054,0.0063,0.9917</t>
+  </si>
+  <si>
+    <t>0.0073,0.0049,0.0025,0.9948</t>
+  </si>
+  <si>
+    <t>0.0010,0.9708,0.6427,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.4676,0.9929,0.0002</t>
+  </si>
+  <si>
+    <t>0.0141,0.8285,0.5360,0.0062</t>
+  </si>
+  <si>
+    <t>0.0074,0.8214,0.8139,0.0027</t>
+  </si>
+  <si>
+    <t>0.0003,0.9793,0.8187,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.8684,0.8514,0.0017</t>
+  </si>
+  <si>
+    <t>0.9777,0.0265,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.9527,0.0672,0.0029,0.0013</t>
+  </si>
+  <si>
+    <t>0.9694,0.0538,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9895,0.0075,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9788,0.0201,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9907,0.0070,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9524,0.0577,0.0045,0.0024</t>
+  </si>
+  <si>
+    <t>0.9791,0.0270,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0011,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0017,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0016,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0013,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9908,0.0036,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.9928,0.0043,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0097,0.0051,0.9703,0.0291</t>
+  </si>
+  <si>
+    <t>0.0796,0.0221,0.8906,0.0217</t>
+  </si>
+  <si>
+    <t>0.7700,0.0095,0.2732,0.0068</t>
+  </si>
+  <si>
+    <t>0.0266,0.0020,0.9865,0.0001</t>
+  </si>
+  <si>
+    <t>0.0285,0.9619,0.0050,0.0008</t>
+  </si>
+  <si>
+    <t>0.0188,0.9640,0.0236,0.0004</t>
+  </si>
+  <si>
+    <t>0.1142,0.9167,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.3718,0.6640,0.0399,0.0032</t>
+  </si>
+  <si>
+    <t>0.0177,0.9746,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.0546,0.9429,0.0088,0.0004</t>
+  </si>
+  <si>
+    <t>0.5737,0.4539,0.0339,0.0012</t>
+  </si>
+  <si>
+    <t>0.7002,0.0973,0.2618,0.0125</t>
+  </si>
+  <si>
+    <t>0.2519,0.0105,0.8274,0.0034</t>
+  </si>
+  <si>
+    <t>0.5068,0.0491,0.3956,0.0591</t>
+  </si>
+  <si>
+    <t>0.4552,0.0256,0.5768,0.0252</t>
+  </si>
+  <si>
+    <t>0.0725,0.0833,0.0603,0.9158</t>
+  </si>
+  <si>
+    <t>0.0149,0.9646,0.0358,0.0012</t>
+  </si>
+  <si>
+    <t>0.0082,0.9733,0.0129,0.0052</t>
+  </si>
+  <si>
+    <t>0.0322,0.9069,0.0296,0.0415</t>
+  </si>
+  <si>
+    <t>0.0004,0.4251,0.9896,0.0006</t>
+  </si>
+  <si>
+    <t>0.0161,0.9731,0.0484,0.0014</t>
+  </si>
+  <si>
+    <t>0.5734,0.3866,0.0664,0.0009</t>
+  </si>
+  <si>
+    <t>0.4989,0.5770,0.0204,0.0027</t>
+  </si>
+  <si>
+    <t>0.9701,0.0142,0.0064,0.0042</t>
+  </si>
+  <si>
+    <t>0.9813,0.0093,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.9889,0.0025,0.0020,0.0021</t>
+  </si>
+  <si>
+    <t>0.9786,0.0050,0.0031,0.0063</t>
+  </si>
+  <si>
+    <t>0.9839,0.0067,0.0012,0.0027</t>
+  </si>
+  <si>
+    <t>0.9548,0.0201,0.0079,0.0074</t>
+  </si>
+  <si>
+    <t>0.9897,0.0042,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9665,0.0062,0.0049,0.0115</t>
+  </si>
+  <si>
+    <t>0.0020,0.5940,0.9756,0.0010</t>
+  </si>
+  <si>
+    <t>0.0018,0.2547,0.9866,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.3964,0.9686,0.0004</t>
+  </si>
+  <si>
+    <t>0.0179,0.3320,0.9108,0.0026</t>
+  </si>
+  <si>
+    <t>0.6734,0.1385,0.1685,0.0388</t>
+  </si>
+  <si>
+    <t>0.2530,0.1027,0.6693,0.0082</t>
+  </si>
+  <si>
+    <t>0.4474,0.0037,0.7715,0.0014</t>
+  </si>
+  <si>
+    <t>0.6953,0.0702,0.2457,0.0181</t>
+  </si>
+  <si>
+    <t>0.8084,0.0035,0.0011,0.2490</t>
+  </si>
+  <si>
+    <t>0.0010,0.0046,0.0009,0.9987</t>
+  </si>
+  <si>
+    <t>0.0144,0.0055,0.0060,0.9902</t>
+  </si>
+  <si>
+    <t>0.0070,0.0009,0.0169,0.9890</t>
+  </si>
+  <si>
+    <t>0.0019,0.6425,0.9182,0.0002</t>
+  </si>
+  <si>
+    <t>0.9792,0.0055,0.0097,0.0024</t>
+  </si>
+  <si>
+    <t>0.9004,0.0439,0.0457,0.0081</t>
+  </si>
+  <si>
+    <t>0.8798,0.0828,0.0103,0.0185</t>
+  </si>
+  <si>
+    <t>0.6187,0.4724,0.0210,0.0018</t>
+  </si>
+  <si>
+    <t>0.9805,0.0073,0.0089,0.0006</t>
+  </si>
+  <si>
+    <t>0.7542,0.0383,0.0466,0.1522</t>
+  </si>
+  <si>
+    <t>0.9801,0.0036,0.0016,0.0055</t>
+  </si>
+  <si>
+    <t>0.0057,0.0299,0.9718,0.0159</t>
+  </si>
+  <si>
+    <t>0.9468,0.0010,0.0091,0.0235</t>
+  </si>
+  <si>
+    <t>0.9779,0.0023,0.0042,0.0057</t>
+  </si>
+  <si>
+    <t>0.1754,0.8194,0.0238,0.0026</t>
+  </si>
+  <si>
+    <t>0.9074,0.0415,0.0221,0.0058</t>
+  </si>
+  <si>
+    <t>0.8832,0.0604,0.0242,0.0083</t>
+  </si>
+  <si>
+    <t>0.3161,0.7004,0.0042,0.0084</t>
+  </si>
+  <si>
+    <t>0.8729,0.0920,0.0244,0.0053</t>
+  </si>
+  <si>
+    <t>0.6054,0.4818,0.0316,0.0122</t>
+  </si>
+  <si>
+    <t>0.9936,0.0017,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9890,0.0037,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9705,0.0228,0.0049,0.0022</t>
+  </si>
+  <si>
+    <t>0.9729,0.0043,0.0174,0.0027</t>
+  </si>
+  <si>
+    <t>0.9835,0.0074,0.0051,0.0011</t>
+  </si>
+  <si>
+    <t>0.9851,0.0064,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.9801,0.0168,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9906,0.0015,0.0004,0.0032</t>
+  </si>
+  <si>
+    <t>0.6579,0.4580,0.0109,0.0046</t>
+  </si>
+  <si>
+    <t>0.3340,0.6098,0.0728,0.0009</t>
+  </si>
+  <si>
+    <t>0.2825,0.8025,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.8901,0.0915,0.0435,0.0082</t>
+  </si>
+  <si>
+    <t>0.7298,0.4210,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.8645,0.0792,0.0725,0.0088</t>
+  </si>
+  <si>
+    <t>0.9749,0.0178,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.8464,0.2432,0.0036,0.0023</t>
+  </si>
+  <si>
+    <t>0.0002,0.0056,0.9982,0.0012</t>
+  </si>
+  <si>
+    <t>0.9044,0.0788,0.0291,0.0022</t>
+  </si>
+  <si>
+    <t>0.0020,0.0065,0.9940,0.0010</t>
+  </si>
+  <si>
+    <t>0.0090,0.1131,0.9541,0.0152</t>
+  </si>
+  <si>
+    <t>0.0147,0.0081,0.9807,0.0008</t>
+  </si>
+  <si>
+    <t>0.0051,0.2568,0.9784,0.0005</t>
+  </si>
+  <si>
+    <t>0.0054,0.0045,0.9888,0.0028</t>
+  </si>
+  <si>
+    <t>0.0044,0.0039,0.9899,0.0015</t>
+  </si>
+  <si>
+    <t>0.0027,0.0021,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.3298,0.1069,0.6183,0.0072</t>
+  </si>
+  <si>
+    <t>0.1323,0.1005,0.8353,0.0083</t>
+  </si>
+  <si>
+    <t>0.2211,0.1295,0.7042,0.0085</t>
+  </si>
+  <si>
+    <t>0.0173,0.9242,0.1078,0.0004</t>
+  </si>
+  <si>
+    <t>0.2232,0.1799,0.5682,0.0041</t>
+  </si>
+  <si>
+    <t>0.1643,0.8195,0.0130,0.0132</t>
+  </si>
+  <si>
+    <t>0.4933,0.0711,0.4690,0.0369</t>
+  </si>
+  <si>
+    <t>0.3911,0.1961,0.5279,0.0161</t>
+  </si>
+  <si>
+    <t>0.4826,0.6890,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.6906,0.4858,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.7114,0.4747,0.0042,0.0003</t>
+  </si>
+  <si>
+    <t>0.8580,0.1977,0.0084,0.0007</t>
+  </si>
+  <si>
+    <t>0.5216,0.6146,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.7016,0.0333,0.3661,0.0030</t>
+  </si>
+  <si>
+    <t>0.6933,0.0124,0.4376,0.0040</t>
+  </si>
+  <si>
+    <t>0.7538,0.0418,0.2034,0.0266</t>
+  </si>
+  <si>
+    <t>0.5601,0.0071,0.4389,0.0383</t>
+  </si>
+  <si>
+    <t>0.4914,0.0258,0.6148,0.0013</t>
+  </si>
+  <si>
+    <t>0.0028,0.0038,0.9889,0.0106</t>
+  </si>
+  <si>
+    <t>0.0950,0.3075,0.7814,0.0516</t>
+  </si>
+  <si>
+    <t>0.0199,0.0627,0.9514,0.0097</t>
+  </si>
+  <si>
+    <t>0.0970,0.0233,0.9254,0.0023</t>
+  </si>
+  <si>
+    <t>0.0373,0.4054,0.6063,0.0037</t>
+  </si>
+  <si>
+    <t>0.9821,0.0163,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9850,0.0066,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0088,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9871,0.0034,0.0015,0.0028</t>
+  </si>
+  <si>
+    <t>0.9734,0.0469,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9797,0.0304,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9887,0.0039,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9855,0.0076,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.2959,0.0128,0.8149,0.0022</t>
+  </si>
+  <si>
+    <t>0.2436,0.5884,0.3120,0.0125</t>
+  </si>
+  <si>
+    <t>0.7265,0.0796,0.1674,0.0287</t>
+  </si>
+  <si>
+    <t>0.0164,0.0107,0.9846,0.0005</t>
+  </si>
+  <si>
+    <t>0.0054,0.0248,0.9838,0.0017</t>
+  </si>
+  <si>
+    <t>0.0843,0.0493,0.8673,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0052,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0769,0.0498,0.8798,0.0036</t>
+  </si>
+  <si>
+    <t>0.0063,0.0080,0.9869,0.0026</t>
+  </si>
+  <si>
+    <t>0.0183,0.0186,0.9769,0.0007</t>
+  </si>
+  <si>
+    <t>0.2899,0.2082,0.5769,0.0386</t>
+  </si>
+  <si>
+    <t>0.8477,0.0021,0.2343,0.0021</t>
+  </si>
+  <si>
+    <t>0.7292,0.0045,0.4014,0.0029</t>
+  </si>
+  <si>
+    <t>0.8393,0.0244,0.1096,0.0100</t>
+  </si>
+  <si>
+    <t>0.9876,0.0070,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9744,0.0495,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9564,0.0700,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9718,0.0238,0.0070,0.0009</t>
+  </si>
+  <si>
+    <t>0.9921,0.0045,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9737,0.0432,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9869,0.0159,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9863,0.0059,0.0010,0.0026</t>
+  </si>
+  <si>
+    <t>0.0348,0.0887,0.9116,0.0018</t>
+  </si>
+  <si>
+    <t>0.0101,0.1707,0.9529,0.0005</t>
+  </si>
+  <si>
+    <t>0.0182,0.0421,0.9608,0.0005</t>
+  </si>
+  <si>
+    <t>0.0952,0.1118,0.7607,0.0012</t>
+  </si>
+  <si>
+    <t>0.0173,0.0067,0.9844,0.0009</t>
+  </si>
+  <si>
+    <t>0.1756,0.0215,0.7587,0.0695</t>
+  </si>
+  <si>
+    <t>0.0574,0.0094,0.9402,0.0039</t>
+  </si>
+  <si>
+    <t>0.1448,0.0384,0.8030,0.0375</t>
+  </si>
+  <si>
+    <t>0.8538,0.0126,0.0389,0.0694</t>
+  </si>
+  <si>
+    <t>0.0376,0.0186,0.0054,0.9776</t>
+  </si>
+  <si>
+    <t>0.0233,0.0019,0.0117,0.9824</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0067,0.0672,0.0028,0.9902</t>
+  </si>
+  <si>
+    <t>0.8059,0.0478,0.0465,0.0619</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2312,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2536,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2581,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3950,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
